--- a/practice/module-4-pivots-and-charts.xlsx
+++ b/practice/module-4-pivots-and-charts.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Defects" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Trend" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Tasks" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Solutions" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +25,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,8 +47,27 @@
       <i val="1"/>
       <color rgb="00666666"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00555555"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -57,6 +77,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="000F6F3F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
   </fills>
@@ -72,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -83,6 +108,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3208,7 +3244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3413,6 +3449,239 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Self-check:</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Right-click any sheet tab → Unhide → Solutions to reveal the answer key. Try every task FIRST without peeking.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Solutions — Module 4 — Charts &amp; PivotTables</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>These are the expected formulas / results for each Tasks sheet item. Try the task FIRST in real Excel, then peek here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Expected solution / formula</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Where it lands</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Verification</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Insert → PivotTable → New Worksheet. Drag: Region → Rows; Product Category → Columns; Revenue → Values (Sum).</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>New sheet</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Pivot shows 4 region rows × 4 category columns + Grand Total row/column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>PivotTable Analyze → Insert Slicer (Salesperson) and Insert Timeline (Order Date). Right-click slicer → Report Connections to verify linkage.</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Same sheet as the pivot</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Clicking a slicer or scrubbing the timeline filters the pivot live.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>PivotTable Analyze → Fields, Items &amp; Sets → Calculated Field → Name: Profit, Formula: = Revenue - Cost</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>PivotTable Values area</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>New 'Sum of Profit' column appears alongside Revenue and is positive for most cells.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Select A1:B9 on Defects → Insert → Insert Statistic Chart → Pareto.</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Defects sheet (chart object)</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Bars in descending order; orange cumulative-% line crosses ~80% near the third bar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Select N2:N5 → Insert → Sparklines → Line. Data Range: B2:M5.</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Trend!N2:N5</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Each row shows a tiny upward-trending line; right-click to add markers if desired.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Click chart series → +'Chart Elements' → Trendline → More Options → Linear, Forward forecast 3 periods, check 'Display Equation' and 'Display R-squared'.</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Trendline on a Region series chart</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Chart shows dotted forecast line + textbox y=mx+b and R² value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Select monthly revenue range → Insert → Waterfall. Right-click the final bar → Set as Total.</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>New chart on Quarterly Sales sheet</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Final bar is grey/black 'Total'; intermediate bars are green/red gain/loss.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Insert → Timeline → Order Date. Use the level dropdown (top-right of the Timeline tile) to switch Months ↔ Quarters ↔ Years.</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Timeline tile</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Switching to Quarters shows Q1–Q4 buckets instead of monthly cells.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
